--- a/src/com/inetBanking/testData/LoginTestData.xlsx
+++ b/src/com/inetBanking/testData/LoginTestData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>username</t>
   </si>
@@ -24,22 +24,10 @@
     <t>password</t>
   </si>
   <si>
-    <t>mngr284542</t>
+    <t>mngr136913</t>
   </si>
   <si>
-    <t>anutAsa</t>
-  </si>
-  <si>
-    <t>mngr284777</t>
-  </si>
-  <si>
-    <t>bUjedAs</t>
-  </si>
-  <si>
-    <t>mngr284820</t>
-  </si>
-  <si>
-    <t>EpAqupA</t>
+    <t>abc321!</t>
   </si>
 </sst>
 </file>
@@ -396,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -419,22 +407,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
